--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17214A5C-03D9-46E0-A048-90C53888B92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9D7AE1-9A57-4EBC-90BB-7BBF075EB1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="74">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -223,6 +223,36 @@
   </si>
   <si>
     <t>«таганскому» исполнению</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и пакет наркотиков</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и посылку наркотиков</t>
+  </si>
+  <si>
+    <t>обширной оперативной информацией, поступавшей</t>
+  </si>
+  <si>
+    <t>обширными незамедлительными сведениями, поступавшими</t>
+  </si>
+  <si>
+    <t>отдыхал крутой авторитет Мансур Шелковников, имевший</t>
+  </si>
+  <si>
+    <t>отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
+  </si>
+  <si>
+    <t>воровской дипломатии, конечная цель которой</t>
+  </si>
+  <si>
+    <t>воровского искусства ведения переговоров, конечная цель которого</t>
+  </si>
+  <si>
+    <t>Реализовать материалы в отношении взяточников</t>
+  </si>
+  <si>
+    <t>Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
   </si>
 </sst>
 </file>
@@ -270,10 +300,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -554,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="1"/>
@@ -737,6 +768,14 @@
         <v>63</v>
       </c>
     </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -744,7 +783,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003C73B8-E647-489E-B76A-27BE5419F554}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="74.1796875" customWidth="1"/>
@@ -773,6 +812,38 @@
       </c>
       <c r="B3" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="6"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5E56A-FC2C-4B9F-8FD2-1219F19B7421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="неизменные_короткие" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="неизменные_длинные" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ошибки" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
+    <sheet name="неизменные" sheetId="2" r:id="rId2"/>
+    <sheet name="неизменные_длинные" sheetId="3" r:id="rId3"/>
+    <sheet name="ошибки" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,147 +31,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
-  <si>
-    <t xml:space="preserve">форма таких «рецензий» иногда немного напрягала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вид таких «оценок» иногда немного напрягал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">брежневской (застойной) конституцией</t>
-  </si>
-  <si>
-    <t xml:space="preserve">брежневским (застойный) постановлением</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разговор Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разговор Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрешил Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрешил Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выразился Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выразился Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">знакомый Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">знакомый Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">расстреляли Гену</t>
-  </si>
-  <si>
-    <t xml:space="preserve">расстреляли Генy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В «лазанской» группировке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В «лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">как Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">как Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанской» группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанского» преступного сообщества</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гена Шрам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Генa Шрам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если бы Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если бы Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">и Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">и Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гены Шрама</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанская» группировка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанское» преступное сообщество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">авторитет же чеченцев возрастал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">личная значимость же чеченцев возрастала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несших «боевую вахту» у кафе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нёсших «боевую вахту» у закусочной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тактика чеченской общины строилась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Под-ход чеченской общины строился</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанской» группировке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">группа московских боевиков избила</t>
-  </si>
-  <si>
-    <t xml:space="preserve">под-раз-деление московских бое-виков из-било</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в программе «Время»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в быдло-показе «Время»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">микроклимат Бутырки подействовал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">внутренние погодные условия Бутырки подействовали</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«таганской» версии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«таганскому» исполнению</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашли в карманах гранату и пакет наркотиков</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашли в карманах гранату и посылку наркотиков</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
+  <si>
+    <t>форма таких «рецензий» иногда немного напрягала</t>
+  </si>
+  <si>
+    <t>вид таких «оценок» иногда немного напрягал</t>
+  </si>
+  <si>
+    <t>брежневской (застойной) конституцией</t>
+  </si>
+  <si>
+    <t>брежневским (застойный) постановлением</t>
+  </si>
+  <si>
+    <t>разговор Гена</t>
+  </si>
+  <si>
+    <t>разговор Генa</t>
+  </si>
+  <si>
+    <t>разрешил Гена</t>
+  </si>
+  <si>
+    <t>разрешил Генa</t>
+  </si>
+  <si>
+    <t>выразился Гена</t>
+  </si>
+  <si>
+    <t>выразился Генa</t>
+  </si>
+  <si>
+    <t>знакомый Гена</t>
+  </si>
+  <si>
+    <t>знакомый Генa</t>
+  </si>
+  <si>
+    <t>расстреляли Гену</t>
+  </si>
+  <si>
+    <t>расстреляли Генy</t>
+  </si>
+  <si>
+    <t>В «лазанской» группировке</t>
+  </si>
+  <si>
+    <t>В «лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>как Гена</t>
+  </si>
+  <si>
+    <t>как Генa</t>
+  </si>
+  <si>
+    <t>«лазанской» группировки</t>
+  </si>
+  <si>
+    <t>«лазанского» преступного сообщества</t>
+  </si>
+  <si>
+    <t>Гена Шрам</t>
+  </si>
+  <si>
+    <t>Генa Шрам</t>
+  </si>
+  <si>
+    <t>Если бы Гена</t>
+  </si>
+  <si>
+    <t>Если бы Генa</t>
+  </si>
+  <si>
+    <t>и Гена</t>
+  </si>
+  <si>
+    <t>и Генa</t>
+  </si>
+  <si>
+    <t>Гены Шрама</t>
+  </si>
+  <si>
+    <t>«лазанская» группировка</t>
+  </si>
+  <si>
+    <t>«лазанское» преступное сообщество</t>
+  </si>
+  <si>
+    <t>авторитет же чеченцев возрастал</t>
+  </si>
+  <si>
+    <t>личная значимость же чеченцев возрастала</t>
+  </si>
+  <si>
+    <t>несших «боевую вахту» у кафе</t>
+  </si>
+  <si>
+    <t>нёсших «боевую вахту» у закусочной</t>
+  </si>
+  <si>
+    <t>Тактика чеченской общины строилась</t>
+  </si>
+  <si>
+    <t>Под-ход чеченской общины строился</t>
+  </si>
+  <si>
+    <t>«лазанской» группировке</t>
+  </si>
+  <si>
+    <t>«лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>группа московских боевиков избила</t>
+  </si>
+  <si>
+    <t>под-раз-деление московских бое-виков из-било</t>
+  </si>
+  <si>
+    <t>в программе «Время»</t>
+  </si>
+  <si>
+    <t>в быдло-показе «Время»</t>
+  </si>
+  <si>
+    <t>микроклимат Бутырки подействовал</t>
+  </si>
+  <si>
+    <t>внутренние погодные условия Бутырки подействовали</t>
+  </si>
+  <si>
+    <t>«таганской» версии</t>
+  </si>
+  <si>
+    <t>«таганскому» исполнению</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и пакет наркотиков</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и посылку наркотиков</t>
   </si>
   <si>
     <t xml:space="preserve">Сидели небольшой компанией, украшал которую
@@ -178,7 +186,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">Сидели небольшим содружеством</t>
+      <t>Сидели небольшим содружеством</t>
     </r>
     <r>
       <rPr>
@@ -188,28 +196,28 @@
         <family val="2"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">, украшал которое</t>
+      <t>, украшал которое</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">роскошь эксплуатировать</t>
-  </si>
-  <si>
-    <t xml:space="preserve">роскошь использовать</t>
+    <t>роскошь эксплуатировать</t>
+  </si>
+  <si>
+    <t>роскошь использовать</t>
   </si>
   <si>
     <t xml:space="preserve">группа качков из Павловского Посада разгромила
 </t>
   </si>
   <si>
-    <t xml:space="preserve">подразделение качков из Павловского Посада разгромило</t>
+    <t>подразделение качков из Павловского Посада разгромило</t>
   </si>
   <si>
     <t xml:space="preserve">зал ресторана гостиницы «Останкинская», считавшийся
 </t>
   </si>
   <si>
-    <t xml:space="preserve">хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
+    <t>хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
   </si>
   <si>
     <t xml:space="preserve">с Герой
@@ -228,46 +236,46 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">могущественной чеченской преступной группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">могущественного чеченского преступного сообщества</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одиннадцатую секцию торговой точки «Автомобили», через которую</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одиннадцатый раздел торговой точки «Автомобили», через который</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасной из них является так называемая чеченская группа, совершающая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обширной оперативной информацией, поступавшей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обширными незамедлительными сведениями, поступавшими</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдыхал крутой авторитет Мансур Шелковников, имевший</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">воровской дипломатии, конечная цель которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">воровского искусства ведения переговоров, конечная цель которого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реализовать материалы в отношении взяточников</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
+    <t>могущественной чеченской преступной группировки</t>
+  </si>
+  <si>
+    <t>могущественного чеченского преступного сообщества</t>
+  </si>
+  <si>
+    <t>одиннадцатую секцию торговой точки «Автомобили», через которую</t>
+  </si>
+  <si>
+    <t>одиннадцатый раздел торговой точки «Автомобили», через который</t>
+  </si>
+  <si>
+    <t>опасной из них является так называемая чеченская группа, совершающая</t>
+  </si>
+  <si>
+    <t>опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
+  </si>
+  <si>
+    <t>обширной оперативной информацией, поступавшей</t>
+  </si>
+  <si>
+    <t>обширными незамедлительными сведениями, поступавшими</t>
+  </si>
+  <si>
+    <t>отдыхал крутой авторитет Мансур Шелковников, имевший</t>
+  </si>
+  <si>
+    <t>отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
+  </si>
+  <si>
+    <t>воровской дипломатии, конечная цель которой</t>
+  </si>
+  <si>
+    <t>воровского искусства ведения переговоров, конечная цель которого</t>
+  </si>
+  <si>
+    <t>Реализовать материалы в отношении взяточников</t>
+  </si>
+  <si>
+    <t>Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
   </si>
   <si>
     <t xml:space="preserve">Многомиллионная армия ГУЛАГа контролировалась и охранялась
@@ -282,19 +290,19 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
+    <t>проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
+  </si>
+  <si>
+    <t>чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
+  </si>
+  <si>
+    <t>чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
+  </si>
+  <si>
+    <t>Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
+  </si>
+  <si>
+    <t>Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
   </si>
   <si>
     <t xml:space="preserve">бросив за барьером пандуса завернутый в клетчатый плед новенький карабин
@@ -312,49 +320,49 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Конфронтация зашла так далеко, что перестала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Противо-стояние зашло так далеко, что перестало быть удобным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">моска бандитская</t>
-  </si>
-  <si>
-    <t xml:space="preserve">директора торговых</t>
-  </si>
-  <si>
-    <t xml:space="preserve">директора торговых учреждений</t>
+    <t>Конфронтация зашла так далеко, что перестала</t>
+  </si>
+  <si>
+    <t>Противо-стояние зашло так далеко, что перестало быть удобным</t>
+  </si>
+  <si>
+    <t>моска бандитская</t>
+  </si>
+  <si>
+    <t>директора торговых</t>
+  </si>
+  <si>
+    <t>директора торговых учреждений</t>
   </si>
   <si>
     <t xml:space="preserve">Атлангериег </t>
   </si>
   <si>
-    <t xml:space="preserve">Атлангериев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">аттракционы Центральном парке культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">аттракционы в Центральном парке культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позвонил ресторан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позвонил в ресторан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">департ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">депорт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">своих сообщнике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">своих сообщников</t>
+    <t>Атлангериев</t>
+  </si>
+  <si>
+    <t>аттракционы Центральном парке культур</t>
+  </si>
+  <si>
+    <t>аттракционы в Центральном парке культур</t>
+  </si>
+  <si>
+    <t>позвонил ресторан</t>
+  </si>
+  <si>
+    <t>позвонил в ресторан</t>
+  </si>
+  <si>
+    <t>департ</t>
+  </si>
+  <si>
+    <t>депорт</t>
+  </si>
+  <si>
+    <t>своих сообщнике</t>
+  </si>
+  <si>
+    <t>своих сообщников</t>
   </si>
   <si>
     <t xml:space="preserve">Ачерез </t>
@@ -375,7 +383,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">любимых</t>
+    <t>любимых</t>
   </si>
   <si>
     <t xml:space="preserve">детей подругой дороге
@@ -400,44 +408,28 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Очем говорили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">О чем говорили</t>
+    <t>Очем говорили</t>
+  </si>
+  <si>
+    <t>О чем говорили</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нереавизуемой </t>
+  </si>
+  <si>
+    <t xml:space="preserve">нереализуемой </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="204"/>
     </font>
     <font>
@@ -465,7 +457,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="LiberEmb"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -478,7 +469,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -486,61 +477,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -582,12 +553,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -619,7 +590,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -643,7 +614,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -703,219 +674,218 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9.6328125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="73.42"/>
+    <col min="1" max="1" width="58.140625" customWidth="1"/>
+    <col min="2" max="2" width="73.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="24.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" ht="27">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -923,7 +893,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
@@ -931,7 +901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" ht="27">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -939,7 +909,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" ht="27">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -947,7 +917,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" ht="27">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -955,7 +925,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" ht="27">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -964,77 +934,69 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9.6328125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="82.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="79.6"/>
+    <col min="1" max="1" width="82.28515625" customWidth="1"/>
+    <col min="2" max="2" width="79.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
@@ -1042,7 +1004,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" ht="27">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -1050,7 +1012,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="27">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
@@ -1059,29 +1021,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.6328125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="137.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="132.72"/>
+    <col min="1" max="1" width="137.42578125" customWidth="1"/>
+    <col min="2" max="2" width="132.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="18">
       <c r="A1" s="6" t="s">
         <v>77</v>
       </c>
@@ -1089,15 +1043,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>79</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" ht="27">
       <c r="A3" s="2" t="s">
         <v>81</v>
       </c>
@@ -1105,7 +1059,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" ht="27">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -1113,8 +1067,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>85</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -1122,82 +1076,74 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="9.6328125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.31"/>
+    <col min="1" max="1" width="50.5703125" customWidth="1"/>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>100</v>
       </c>
@@ -1205,7 +1151,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="27">
       <c r="A9" s="2" t="s">
         <v>102</v>
       </c>
@@ -1213,7 +1159,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="27">
       <c r="A10" s="2" t="s">
         <v>104</v>
       </c>
@@ -1221,7 +1167,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" ht="27">
       <c r="A11" s="2" t="s">
         <v>106</v>
       </c>
@@ -1229,7 +1175,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>108</v>
       </c>
@@ -1237,7 +1183,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" ht="27">
       <c r="A13" s="2" t="s">
         <v>110</v>
       </c>
@@ -1245,7 +1191,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>112</v>
       </c>
@@ -1253,13 +1199,16 @@
         <v>113</v>
       </c>
     </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -1,28 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB5E56A-FC2C-4B9F-8FD2-1219F19B7421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
-    <sheet name="неизменные" sheetId="2" r:id="rId2"/>
-    <sheet name="неизменные_длинные" sheetId="3" r:id="rId3"/>
-    <sheet name="ошибки" sheetId="4" r:id="rId4"/>
+    <sheet name="неизменные_короткие" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="неизменные_длинные" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ошибки" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -31,147 +23,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
-  <si>
-    <t>форма таких «рецензий» иногда немного напрягала</t>
-  </si>
-  <si>
-    <t>вид таких «оценок» иногда немного напрягал</t>
-  </si>
-  <si>
-    <t>брежневской (застойной) конституцией</t>
-  </si>
-  <si>
-    <t>брежневским (застойный) постановлением</t>
-  </si>
-  <si>
-    <t>разговор Гена</t>
-  </si>
-  <si>
-    <t>разговор Генa</t>
-  </si>
-  <si>
-    <t>разрешил Гена</t>
-  </si>
-  <si>
-    <t>разрешил Генa</t>
-  </si>
-  <si>
-    <t>выразился Гена</t>
-  </si>
-  <si>
-    <t>выразился Генa</t>
-  </si>
-  <si>
-    <t>знакомый Гена</t>
-  </si>
-  <si>
-    <t>знакомый Генa</t>
-  </si>
-  <si>
-    <t>расстреляли Гену</t>
-  </si>
-  <si>
-    <t>расстреляли Генy</t>
-  </si>
-  <si>
-    <t>В «лазанской» группировке</t>
-  </si>
-  <si>
-    <t>В «лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t>как Гена</t>
-  </si>
-  <si>
-    <t>как Генa</t>
-  </si>
-  <si>
-    <t>«лазанской» группировки</t>
-  </si>
-  <si>
-    <t>«лазанского» преступного сообщества</t>
-  </si>
-  <si>
-    <t>Гена Шрам</t>
-  </si>
-  <si>
-    <t>Генa Шрам</t>
-  </si>
-  <si>
-    <t>Если бы Гена</t>
-  </si>
-  <si>
-    <t>Если бы Генa</t>
-  </si>
-  <si>
-    <t>и Гена</t>
-  </si>
-  <si>
-    <t>и Генa</t>
-  </si>
-  <si>
-    <t>Гены Шрама</t>
-  </si>
-  <si>
-    <t>«лазанская» группировка</t>
-  </si>
-  <si>
-    <t>«лазанское» преступное сообщество</t>
-  </si>
-  <si>
-    <t>авторитет же чеченцев возрастал</t>
-  </si>
-  <si>
-    <t>личная значимость же чеченцев возрастала</t>
-  </si>
-  <si>
-    <t>несших «боевую вахту» у кафе</t>
-  </si>
-  <si>
-    <t>нёсших «боевую вахту» у закусочной</t>
-  </si>
-  <si>
-    <t>Тактика чеченской общины строилась</t>
-  </si>
-  <si>
-    <t>Под-ход чеченской общины строился</t>
-  </si>
-  <si>
-    <t>«лазанской» группировке</t>
-  </si>
-  <si>
-    <t>«лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t>группа московских боевиков избила</t>
-  </si>
-  <si>
-    <t>под-раз-деление московских бое-виков из-било</t>
-  </si>
-  <si>
-    <t>в программе «Время»</t>
-  </si>
-  <si>
-    <t>в быдло-показе «Время»</t>
-  </si>
-  <si>
-    <t>микроклимат Бутырки подействовал</t>
-  </si>
-  <si>
-    <t>внутренние погодные условия Бутырки подействовали</t>
-  </si>
-  <si>
-    <t>«таганской» версии</t>
-  </si>
-  <si>
-    <t>«таганскому» исполнению</t>
-  </si>
-  <si>
-    <t>нашли в карманах гранату и пакет наркотиков</t>
-  </si>
-  <si>
-    <t>нашли в карманах гранату и посылку наркотиков</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">форма таких «рецензий» иногда немного напрягала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вид таких «оценок» иногда немного напрягал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">брежневской (застойной) конституцией</t>
+  </si>
+  <si>
+    <t xml:space="preserve">брежневским (застойный) постановлением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">разговор Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">разговор Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">разрешил Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">разрешил Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выразился Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выразился Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">знакомый Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">знакомый Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">расстреляли Гену</t>
+  </si>
+  <si>
+    <t xml:space="preserve">расстреляли Генy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В «лазанской» группировке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В «лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">как Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">как Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанской» группировки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанского» преступного сообщества</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гена Шрам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Генa Шрам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если бы Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если бы Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">и Гена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">и Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гены Шрама</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанская» группировка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанское» преступное сообщество</t>
+  </si>
+  <si>
+    <t xml:space="preserve">авторитет же чеченцев возрастал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">личная значимость же чеченцев возрастала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">несших «боевую вахту» у кафе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нёсших «боевую вахту» у закусочной</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тактика чеченской общины строилась</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Под-ход чеченской общины строился</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанской» группировке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">группа московских боевиков избила</t>
+  </si>
+  <si>
+    <t xml:space="preserve">под-раз-деление московских бое-виков из-било</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в программе «Время»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в быдло-показе «Время»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">микроклимат Бутырки подействовал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">внутренние погодные условия Бутырки подействовали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«таганской» версии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«таганскому» исполнению</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нашли в карманах гранату и пакет наркотиков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">нашли в карманах гранату и посылку наркотиков</t>
   </si>
   <si>
     <t xml:space="preserve">Сидели небольшой компанией, украшал которую
@@ -186,7 +178,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t>Сидели небольшим содружеством</t>
+      <t xml:space="preserve">Сидели небольшим содружеством</t>
     </r>
     <r>
       <rPr>
@@ -196,28 +188,28 @@
         <family val="2"/>
         <charset val="204"/>
       </rPr>
-      <t>, украшал которое</t>
+      <t xml:space="preserve">, украшал которое</t>
     </r>
   </si>
   <si>
-    <t>роскошь эксплуатировать</t>
-  </si>
-  <si>
-    <t>роскошь использовать</t>
+    <t xml:space="preserve">роскошь эксплуатировать</t>
+  </si>
+  <si>
+    <t xml:space="preserve">роскошь использовать</t>
   </si>
   <si>
     <t xml:space="preserve">группа качков из Павловского Посада разгромила
 </t>
   </si>
   <si>
-    <t>подразделение качков из Павловского Посада разгромило</t>
+    <t xml:space="preserve">подразделение качков из Павловского Посада разгромило</t>
   </si>
   <si>
     <t xml:space="preserve">зал ресторана гостиницы «Останкинская», считавшийся
 </t>
   </si>
   <si>
-    <t>хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
+    <t xml:space="preserve">хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
   </si>
   <si>
     <t xml:space="preserve">с Герой
@@ -236,46 +228,46 @@
 </t>
   </si>
   <si>
-    <t>могущественной чеченской преступной группировки</t>
-  </si>
-  <si>
-    <t>могущественного чеченского преступного сообщества</t>
-  </si>
-  <si>
-    <t>одиннадцатую секцию торговой точки «Автомобили», через которую</t>
-  </si>
-  <si>
-    <t>одиннадцатый раздел торговой точки «Автомобили», через который</t>
-  </si>
-  <si>
-    <t>опасной из них является так называемая чеченская группа, совершающая</t>
-  </si>
-  <si>
-    <t>опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
-  </si>
-  <si>
-    <t>обширной оперативной информацией, поступавшей</t>
-  </si>
-  <si>
-    <t>обширными незамедлительными сведениями, поступавшими</t>
-  </si>
-  <si>
-    <t>отдыхал крутой авторитет Мансур Шелковников, имевший</t>
-  </si>
-  <si>
-    <t>отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
-  </si>
-  <si>
-    <t>воровской дипломатии, конечная цель которой</t>
-  </si>
-  <si>
-    <t>воровского искусства ведения переговоров, конечная цель которого</t>
-  </si>
-  <si>
-    <t>Реализовать материалы в отношении взяточников</t>
-  </si>
-  <si>
-    <t>Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
+    <t xml:space="preserve">могущественной чеченской преступной группировки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">могущественного чеченского преступного сообщества</t>
+  </si>
+  <si>
+    <t xml:space="preserve">одиннадцатую секцию торговой точки «Автомобили», через которую</t>
+  </si>
+  <si>
+    <t xml:space="preserve">одиннадцатый раздел торговой точки «Автомобили», через который</t>
+  </si>
+  <si>
+    <t xml:space="preserve">опасной из них является так называемая чеченская группа, совершающая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">обширной оперативной информацией, поступавшей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">обширными незамедлительными сведениями, поступавшими</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отдыхал крутой авторитет Мансур Шелковников, имевший</t>
+  </si>
+  <si>
+    <t xml:space="preserve">отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">воровской дипломатии, конечная цель которой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">воровского искусства ведения переговоров, конечная цель которого</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать материалы в отношении взяточников</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
   </si>
   <si>
     <t xml:space="preserve">Многомиллионная армия ГУЛАГа контролировалась и охранялась
@@ -290,19 +282,26 @@
 </t>
   </si>
   <si>
-    <t>проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
-  </si>
-  <si>
-    <t>чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
-  </si>
-  <si>
-    <t>чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
-  </si>
-  <si>
-    <t>Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
-  </si>
-  <si>
-    <t>Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
+    <t xml:space="preserve">проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
+  </si>
+  <si>
+    <t xml:space="preserve">элитные подразделения спецназа и антитеррористических групп
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">знатные подразделения особого назначения и противо-кровавых отрядов </t>
+  </si>
+  <si>
+    <t xml:space="preserve">чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
   </si>
   <si>
     <t xml:space="preserve">бросив за барьером пандуса завернутый в клетчатый плед новенький карабин
@@ -320,49 +319,49 @@
 </t>
   </si>
   <si>
-    <t>Конфронтация зашла так далеко, что перестала</t>
-  </si>
-  <si>
-    <t>Противо-стояние зашло так далеко, что перестало быть удобным</t>
-  </si>
-  <si>
-    <t>моска бандитская</t>
-  </si>
-  <si>
-    <t>директора торговых</t>
-  </si>
-  <si>
-    <t>директора торговых учреждений</t>
+    <t xml:space="preserve">Конфронтация зашла так далеко, что перестала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Противо-стояние зашло так далеко, что перестало быть удобным</t>
+  </si>
+  <si>
+    <t xml:space="preserve">моска бандитская</t>
+  </si>
+  <si>
+    <t xml:space="preserve">директора торговых</t>
+  </si>
+  <si>
+    <t xml:space="preserve">директора торговых учреждений</t>
   </si>
   <si>
     <t xml:space="preserve">Атлангериег </t>
   </si>
   <si>
-    <t>Атлангериев</t>
-  </si>
-  <si>
-    <t>аттракционы Центральном парке культур</t>
-  </si>
-  <si>
-    <t>аттракционы в Центральном парке культур</t>
-  </si>
-  <si>
-    <t>позвонил ресторан</t>
-  </si>
-  <si>
-    <t>позвонил в ресторан</t>
-  </si>
-  <si>
-    <t>департ</t>
-  </si>
-  <si>
-    <t>депорт</t>
-  </si>
-  <si>
-    <t>своих сообщнике</t>
-  </si>
-  <si>
-    <t>своих сообщников</t>
+    <t xml:space="preserve">Атлангериев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">аттракционы Центральном парке культур</t>
+  </si>
+  <si>
+    <t xml:space="preserve">аттракционы в Центральном парке культур</t>
+  </si>
+  <si>
+    <t xml:space="preserve">позвонил ресторан</t>
+  </si>
+  <si>
+    <t xml:space="preserve">позвонил в ресторан</t>
+  </si>
+  <si>
+    <t xml:space="preserve">департ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">депорт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">своих сообщнике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">своих сообщников</t>
   </si>
   <si>
     <t xml:space="preserve">Ачерез </t>
@@ -383,7 +382,7 @@
 </t>
   </si>
   <si>
-    <t>любимых</t>
+    <t xml:space="preserve">любимых</t>
   </si>
   <si>
     <t xml:space="preserve">детей подругой дороге
@@ -408,10 +407,10 @@
 </t>
   </si>
   <si>
-    <t>Очем говорили</t>
-  </si>
-  <si>
-    <t>О чем говорили</t>
+    <t xml:space="preserve">Очем говорили</t>
+  </si>
+  <si>
+    <t xml:space="preserve">О чем говорили</t>
   </si>
   <si>
     <t xml:space="preserve">нереавизуемой </t>
@@ -423,14 +422,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -457,6 +475,7 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="LiberEmb"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -469,7 +488,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -477,41 +496,74 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -553,12 +605,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -590,7 +642,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -614,7 +666,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -674,250 +726,251 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="58.140625" customWidth="1"/>
-    <col min="2" max="2" width="73.42578125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="73.43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="27">
+    <row r="25" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="27">
+    <row r="27" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="27">
+    <row r="28" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="27">
+    <row r="29" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -925,7 +978,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="27">
+    <row r="30" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -934,77 +987,85 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="82.28515625" customWidth="1"/>
-    <col min="2" max="2" width="79.5703125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="82.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="79.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="27">
+    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -1012,203 +1073,232 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>76</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="24.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="137.42578125" customWidth="1"/>
-    <col min="2" max="2" width="132.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="137.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="132.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18">
-      <c r="A1" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B1" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="27">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="27">
+        <v>83</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="7" t="s">
         <v>86</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="50.5703125" customWidth="1"/>
-    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B3" s="0" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B4" s="0" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B5" s="0" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B6" s="0" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B7" s="0" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="27">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="27">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="27">
+        <v>106</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="27">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001886CD-CCEA-4EB4-A172-A2F43888478F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="неизменные_короткие" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="неизменные_длинные" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ошибки" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
+    <sheet name="неизменные" sheetId="2" r:id="rId2"/>
+    <sheet name="неизменные_длинные" sheetId="3" r:id="rId3"/>
+    <sheet name="ошибки" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,147 +31,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
-  <si>
-    <t xml:space="preserve">форма таких «рецензий» иногда немного напрягала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вид таких «оценок» иногда немного напрягал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">брежневской (застойной) конституцией</t>
-  </si>
-  <si>
-    <t xml:space="preserve">брежневским (застойный) постановлением</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разговор Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разговор Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрешил Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">разрешил Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выразился Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">выразился Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">знакомый Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">знакомый Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">расстреляли Гену</t>
-  </si>
-  <si>
-    <t xml:space="preserve">расстреляли Генy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В «лазанской» группировке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В «лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">как Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">как Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанской» группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанского» преступного сообщества</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гена Шрам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Генa Шрам</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если бы Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Если бы Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">и Гена</t>
-  </si>
-  <si>
-    <t xml:space="preserve">и Генa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гены Шрама</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанская» группировка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанское» преступное сообщество</t>
-  </si>
-  <si>
-    <t xml:space="preserve">авторитет же чеченцев возрастал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">личная значимость же чеченцев возрастала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">несших «боевую вахту» у кафе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нёсших «боевую вахту» у закусочной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тактика чеченской общины строилась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Под-ход чеченской общины строился</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанской» группировке</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«лазанском» преступном сообществе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">группа московских боевиков избила</t>
-  </si>
-  <si>
-    <t xml:space="preserve">под-раз-деление московских бое-виков из-било</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в программе «Время»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в быдло-показе «Время»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">микроклимат Бутырки подействовал</t>
-  </si>
-  <si>
-    <t xml:space="preserve">внутренние погодные условия Бутырки подействовали</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«таганской» версии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«таганскому» исполнению</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашли в карманах гранату и пакет наркотиков</t>
-  </si>
-  <si>
-    <t xml:space="preserve">нашли в карманах гранату и посылку наркотиков</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+  <si>
+    <t>форма таких «рецензий» иногда немного напрягала</t>
+  </si>
+  <si>
+    <t>вид таких «оценок» иногда немного напрягал</t>
+  </si>
+  <si>
+    <t>брежневской (застойной) конституцией</t>
+  </si>
+  <si>
+    <t>брежневским (застойный) постановлением</t>
+  </si>
+  <si>
+    <t>разговор Гена</t>
+  </si>
+  <si>
+    <t>разговор Генa</t>
+  </si>
+  <si>
+    <t>разрешил Гена</t>
+  </si>
+  <si>
+    <t>разрешил Генa</t>
+  </si>
+  <si>
+    <t>выразился Гена</t>
+  </si>
+  <si>
+    <t>выразился Генa</t>
+  </si>
+  <si>
+    <t>знакомый Гена</t>
+  </si>
+  <si>
+    <t>знакомый Генa</t>
+  </si>
+  <si>
+    <t>расстреляли Гену</t>
+  </si>
+  <si>
+    <t>расстреляли Генy</t>
+  </si>
+  <si>
+    <t>В «лазанской» группировке</t>
+  </si>
+  <si>
+    <t>В «лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>как Гена</t>
+  </si>
+  <si>
+    <t>как Генa</t>
+  </si>
+  <si>
+    <t>«лазанской» группировки</t>
+  </si>
+  <si>
+    <t>«лазанского» преступного сообщества</t>
+  </si>
+  <si>
+    <t>Гена Шрам</t>
+  </si>
+  <si>
+    <t>Генa Шрам</t>
+  </si>
+  <si>
+    <t>Если бы Гена</t>
+  </si>
+  <si>
+    <t>Если бы Генa</t>
+  </si>
+  <si>
+    <t>и Гена</t>
+  </si>
+  <si>
+    <t>и Генa</t>
+  </si>
+  <si>
+    <t>Гены Шрама</t>
+  </si>
+  <si>
+    <t>«лазанская» группировка</t>
+  </si>
+  <si>
+    <t>«лазанское» преступное сообщество</t>
+  </si>
+  <si>
+    <t>авторитет же чеченцев возрастал</t>
+  </si>
+  <si>
+    <t>личная значимость же чеченцев возрастала</t>
+  </si>
+  <si>
+    <t>несших «боевую вахту» у кафе</t>
+  </si>
+  <si>
+    <t>нёсших «боевую вахту» у закусочной</t>
+  </si>
+  <si>
+    <t>Тактика чеченской общины строилась</t>
+  </si>
+  <si>
+    <t>Под-ход чеченской общины строился</t>
+  </si>
+  <si>
+    <t>«лазанской» группировке</t>
+  </si>
+  <si>
+    <t>«лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>группа московских боевиков избила</t>
+  </si>
+  <si>
+    <t>под-раз-деление московских бое-виков из-било</t>
+  </si>
+  <si>
+    <t>в программе «Время»</t>
+  </si>
+  <si>
+    <t>в быдло-показе «Время»</t>
+  </si>
+  <si>
+    <t>микроклимат Бутырки подействовал</t>
+  </si>
+  <si>
+    <t>внутренние погодные условия Бутырки подействовали</t>
+  </si>
+  <si>
+    <t>«таганской» версии</t>
+  </si>
+  <si>
+    <t>«таганскому» исполнению</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и пакет наркотиков</t>
+  </si>
+  <si>
+    <t>нашли в карманах гранату и посылку наркотиков</t>
   </si>
   <si>
     <t xml:space="preserve">Сидели небольшой компанией, украшал которую
@@ -178,7 +186,7 @@
         <family val="1"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">Сидели небольшим содружеством</t>
+      <t>Сидели небольшим содружеством</t>
     </r>
     <r>
       <rPr>
@@ -188,28 +196,28 @@
         <family val="2"/>
         <charset val="204"/>
       </rPr>
-      <t xml:space="preserve">, украшал которое</t>
+      <t>, украшал которое</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">роскошь эксплуатировать</t>
-  </si>
-  <si>
-    <t xml:space="preserve">роскошь использовать</t>
+    <t>роскошь эксплуатировать</t>
+  </si>
+  <si>
+    <t>роскошь использовать</t>
   </si>
   <si>
     <t xml:space="preserve">группа качков из Павловского Посада разгромила
 </t>
   </si>
   <si>
-    <t xml:space="preserve">подразделение качков из Павловского Посада разгромило</t>
+    <t>подразделение качков из Павловского Посада разгромило</t>
   </si>
   <si>
     <t xml:space="preserve">зал ресторана гостиницы «Останкинская», считавшийся
 </t>
   </si>
   <si>
-    <t xml:space="preserve">хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
+    <t>хоромы харчёвни для дворян гостиницы «Останкинская», считавшимися</t>
   </si>
   <si>
     <t xml:space="preserve">с Герой
@@ -228,46 +236,46 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">могущественной чеченской преступной группировки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">могущественного чеченского преступного сообщества</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одиннадцатую секцию торговой точки «Автомобили», через которую</t>
-  </si>
-  <si>
-    <t xml:space="preserve">одиннадцатый раздел торговой точки «Автомобили», через который</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасной из них является так называемая чеченская группа, совершающая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обширной оперативной информацией, поступавшей</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обширными незамедлительными сведениями, поступавшими</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдыхал крутой авторитет Мансур Шелковников, имевший</t>
-  </si>
-  <si>
-    <t xml:space="preserve">отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">воровской дипломатии, конечная цель которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">воровского искусства ведения переговоров, конечная цель которого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реализовать материалы в отношении взяточников</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
+    <t>могущественной чеченской преступной группировки</t>
+  </si>
+  <si>
+    <t>могущественного чеченского преступного сообщества</t>
+  </si>
+  <si>
+    <t>одиннадцатую секцию торговой точки «Автомобили», через которую</t>
+  </si>
+  <si>
+    <t>одиннадцатый раздел торговой точки «Автомобили», через который</t>
+  </si>
+  <si>
+    <t>опасной из них является так называемая чеченская группа, совершающая</t>
+  </si>
+  <si>
+    <t>опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
+  </si>
+  <si>
+    <t>обширной оперативной информацией, поступавшей</t>
+  </si>
+  <si>
+    <t>обширными незамедлительными сведениями, поступавшими</t>
+  </si>
+  <si>
+    <t>отдыхал крутой авторитет Мансур Шелковников, имевший</t>
+  </si>
+  <si>
+    <t>отдыхалокрутое лицо,обладающее значимостью Мансур Шелковников, имевшее</t>
+  </si>
+  <si>
+    <t>воровской дипломатии, конечная цель которой</t>
+  </si>
+  <si>
+    <t>воровского искусства ведения переговоров, конечная цель которого</t>
+  </si>
+  <si>
+    <t>Реализовать материалы в отношении взяточников</t>
+  </si>
+  <si>
+    <t>Обнародовать доказательства о совершении преступлений в отношении взяточников</t>
   </si>
   <si>
     <t xml:space="preserve">Многомиллионная армия ГУЛАГа контролировалась и охранялась
@@ -282,7 +290,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
+    <t>проведенной воеводой Ермоловым подхода выжженной земли, принёсшим</t>
   </si>
   <si>
     <t xml:space="preserve">элитные подразделения спецназа и антитеррористических групп
@@ -292,16 +300,16 @@
     <t xml:space="preserve">знатные подразделения особого назначения и противо-кровавых отрядов </t>
   </si>
   <si>
-    <t xml:space="preserve">чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
+    <t>чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
+  </si>
+  <si>
+    <t>чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
+  </si>
+  <si>
+    <t>Выехавшая на место происшествия оперативная группа милиции едва не опоздала</t>
+  </si>
+  <si>
+    <t>Выехавшее на место происшествия сыскное подразделение милиции едва не опоздало</t>
   </si>
   <si>
     <t xml:space="preserve">бросив за барьером пандуса завернутый в клетчатый плед новенький карабин
@@ -319,49 +327,49 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Конфронтация зашла так далеко, что перестала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Противо-стояние зашло так далеко, что перестало быть удобным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">моска бандитская</t>
-  </si>
-  <si>
-    <t xml:space="preserve">директора торговых</t>
-  </si>
-  <si>
-    <t xml:space="preserve">директора торговых учреждений</t>
+    <t>Конфронтация зашла так далеко, что перестала</t>
+  </si>
+  <si>
+    <t>Противо-стояние зашло так далеко, что перестало быть удобным</t>
+  </si>
+  <si>
+    <t>моска бандитская</t>
+  </si>
+  <si>
+    <t>директора торговых</t>
+  </si>
+  <si>
+    <t>директора торговых учреждений</t>
   </si>
   <si>
     <t xml:space="preserve">Атлангериег </t>
   </si>
   <si>
-    <t xml:space="preserve">Атлангериев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">аттракционы Центральном парке культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">аттракционы в Центральном парке культур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позвонил ресторан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позвонил в ресторан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">департ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">депорт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">своих сообщнике</t>
-  </si>
-  <si>
-    <t xml:space="preserve">своих сообщников</t>
+    <t>Атлангериев</t>
+  </si>
+  <si>
+    <t>аттракционы Центральном парке культур</t>
+  </si>
+  <si>
+    <t>аттракционы в Центральном парке культур</t>
+  </si>
+  <si>
+    <t>позвонил ресторан</t>
+  </si>
+  <si>
+    <t>позвонил в ресторан</t>
+  </si>
+  <si>
+    <t>департ</t>
+  </si>
+  <si>
+    <t>депорт</t>
+  </si>
+  <si>
+    <t>своих сообщнике</t>
+  </si>
+  <si>
+    <t>своих сообщников</t>
   </si>
   <si>
     <t xml:space="preserve">Ачерез </t>
@@ -382,7 +390,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">любимых</t>
+    <t>любимых</t>
   </si>
   <si>
     <t xml:space="preserve">детей подругой дороге
@@ -407,48 +415,32 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Очем говорили</t>
-  </si>
-  <si>
-    <t xml:space="preserve">О чем говорили</t>
+    <t>Очем говорили</t>
+  </si>
+  <si>
+    <t>О чем говорили</t>
   </si>
   <si>
     <t xml:space="preserve">нереавизуемой </t>
   </si>
   <si>
     <t xml:space="preserve">нереализуемой </t>
+  </si>
+  <si>
+    <t>Гeны Шрaмa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -475,7 +467,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="LiberEmb"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -488,7 +479,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -496,74 +487,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -605,12 +562,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -642,7 +599,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -666,7 +623,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -726,219 +683,218 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="73.43"/>
+    <col min="1" max="1" width="58.08984375" customWidth="1"/>
+    <col min="2" max="2" width="73.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:2" ht="26.5">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -946,7 +902,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
@@ -954,7 +910,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:2" ht="26.5">
       <c r="A27" s="2" t="s">
         <v>51</v>
       </c>
@@ -962,7 +918,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:2" ht="26.5">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -970,7 +926,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:2" ht="26.5">
       <c r="A29" s="2" t="s">
         <v>55</v>
       </c>
@@ -978,7 +934,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:2" ht="26.5">
       <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
@@ -987,77 +943,69 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="82.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="79.57"/>
+    <col min="1" max="1" width="82.26953125" customWidth="1"/>
+    <col min="2" max="2" width="79.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>71</v>
       </c>
@@ -1065,7 +1013,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" ht="26.5">
       <c r="A8" s="2" t="s">
         <v>73</v>
       </c>
@@ -1073,7 +1021,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="26.5">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
@@ -1081,7 +1029,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="24.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="26.5">
       <c r="A10" s="2" t="s">
         <v>77</v>
       </c>
@@ -1090,29 +1038,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="137.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="132.71"/>
+    <col min="1" max="1" width="137.453125" customWidth="1"/>
+    <col min="2" max="2" width="132.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="17.5">
       <c r="A1" s="5" t="s">
         <v>79</v>
       </c>
@@ -1120,15 +1060,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" ht="26.5">
       <c r="A3" s="2" t="s">
         <v>83</v>
       </c>
@@ -1136,7 +1076,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" ht="26.5">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
@@ -1144,8 +1084,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1153,82 +1093,74 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="9.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.54296875" defaultRowHeight="14.5"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.29"/>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="49.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
         <v>102</v>
       </c>
@@ -1236,7 +1168,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" ht="26.5">
       <c r="A9" s="2" t="s">
         <v>104</v>
       </c>
@@ -1244,7 +1176,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" ht="26.5">
       <c r="A10" s="2" t="s">
         <v>106</v>
       </c>
@@ -1252,7 +1184,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" ht="26.5">
       <c r="A11" s="2" t="s">
         <v>108</v>
       </c>
@@ -1260,7 +1192,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
         <v>110</v>
       </c>
@@ -1268,7 +1200,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" ht="26.5">
       <c r="A13" s="2" t="s">
         <v>112</v>
       </c>
@@ -1276,7 +1208,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>114</v>
       </c>
@@ -1284,7 +1216,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>116</v>
       </c>
@@ -1293,12 +1225,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>